--- a/analisi_spese_sardi.xlsx
+++ b/analisi_spese_sardi.xlsx
@@ -4524,7 +4524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>70.6353</v>
+        <v>62.9906</v>
       </c>
     </row>
     <row r="7">
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>168.3804</v>
+        <v>402.4275</v>
       </c>
     </row>
     <row r="8">
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>417.1123</v>
+        <v>423.1428</v>
       </c>
     </row>
     <row r="9">
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>45.0473</v>
+        <v>43.0634</v>
       </c>
     </row>
     <row r="11">
@@ -4660,11 +4660,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8-14</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>695.5381</v>
+        <v>360</v>
       </c>
     </row>
     <row r="12">
@@ -4675,26 +4675,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15-30</t>
+          <t>8-14</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>957.6271</v>
+        <v>695.5381</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ITALIA</t>
+          <t>SARDEGNA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>15-30</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>49.915</v>
+        <v>957.6271</v>
       </c>
     </row>
     <row r="14">
@@ -4705,11 +4705,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>152.9562</v>
+        <v>40.6438</v>
       </c>
     </row>
     <row r="15">
@@ -4720,11 +4720,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8-14</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1213.8554</v>
+        <v>658.2896</v>
       </c>
     </row>
     <row r="16">
@@ -4735,26 +4735,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15-30</t>
+          <t>8-14</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>892.3253</v>
+        <v>1019.2771</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ESTERO</t>
+          <t>ITALIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>15-30</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>445.7831</v>
+        <v>892.3253</v>
       </c>
     </row>
     <row r="18">
@@ -4765,11 +4765,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>347.4576</v>
+        <v>409.6386</v>
       </c>
     </row>
     <row r="19">
@@ -4780,11 +4780,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8-14</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>165.9642</v>
+        <v>317.7613</v>
       </c>
     </row>
     <row r="20">
@@ -4795,50 +4795,50 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>8-14</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>162.2706</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ESTERO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>15-30</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>4629.1834</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Tabella STPG pesata</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>segmento</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>classe_durata_soggiorno</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>totale</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TOTALE</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1-3</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>24.2076</v>
       </c>
     </row>
     <row r="25">
@@ -4849,11 +4849,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>33.6761</v>
+        <v>23.8014</v>
       </c>
     </row>
     <row r="26">
@@ -4864,11 +4864,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>8-14</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>41.9073</v>
+        <v>80.4855</v>
       </c>
     </row>
     <row r="27">
@@ -4879,26 +4879,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15-30</t>
+          <t>8-14</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>138.7805</v>
+        <v>41.5546</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SARDEGNA</t>
+          <t>TOTALE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>15-30</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15.399</v>
+        <v>138.7805</v>
       </c>
     </row>
     <row r="29">
@@ -4909,11 +4909,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8-14</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>64.4769</v>
+        <v>14.9534</v>
       </c>
     </row>
     <row r="30">
@@ -4924,41 +4924,41 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15-30</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>40.7207</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ITALIA</t>
+          <t>SARDEGNA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>8-14</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>16.6383</v>
+        <v>64.4769</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ITALIA</t>
+          <t>SARDEGNA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>15-30</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>30.407</v>
+        <v>40.7207</v>
       </c>
     </row>
     <row r="33">
@@ -4969,11 +4969,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8-14</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>134.8728</v>
+        <v>15.6499</v>
       </c>
     </row>
     <row r="34">
@@ -4984,41 +4984,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15-30</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38.2425</v>
+        <v>123.8099</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ESTERO</t>
+          <t>ITALIA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>8-14</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>222.8916</v>
+        <v>106.1747</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ESTERO</t>
+          <t>ITALIA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>15-30</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>74.74930000000001</v>
+        <v>38.2425</v>
       </c>
     </row>
     <row r="37">
@@ -5029,11 +5029,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8-14</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.961</v>
+        <v>175.5594</v>
       </c>
     </row>
     <row r="38">
@@ -5044,138 +5044,102 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>4-7</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>64.3379</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ESTERO</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>8-14</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.1345</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ESTERO</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>15-30</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C40" t="n">
         <v>268.7913</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>2. STP e STPG per categoria in funzione delle classi di durata soggiorno per chi va in Sardegna</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Tabella STP pesata</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>segmento</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>classe_durata_soggiorno</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>totale</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>spese_trasporto_interno</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>spese_alloggio</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>spese_alimentazione</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>spese_ristorazione</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>spese_souvenir</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="I44" s="3" t="inlineStr">
         <is>
           <t>spese_altre</t>
         </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>SARDEGNA</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>1-3</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>45.0473</v>
-      </c>
-      <c r="D43" t="n">
-        <v>6.4709</v>
-      </c>
-      <c r="E43" t="n">
-        <v>11.6974</v>
-      </c>
-      <c r="F43" t="n">
-        <v>9.9552</v>
-      </c>
-      <c r="G43" t="n">
-        <v>6.4709</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>10.453</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>SARDEGNA</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>8-14</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>695.5381</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>157.4803</v>
-      </c>
-      <c r="F44" t="n">
-        <v>39.3701</v>
-      </c>
-      <c r="G44" t="n">
-        <v>498.6877</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -5186,181 +5150,313 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>43.0634</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8.509499999999999</v>
+      </c>
+      <c r="E45" t="n">
+        <v>7.2202</v>
+      </c>
+      <c r="F45" t="n">
+        <v>10.3146</v>
+      </c>
+      <c r="G45" t="n">
+        <v>8.2517</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>8.7674</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SARDEGNA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>4-7</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>360</v>
+      </c>
+      <c r="D46" t="n">
+        <v>60</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>100</v>
+      </c>
+      <c r="G46" t="n">
+        <v>200</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SARDEGNA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>8-14</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>695.5381</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>157.4803</v>
+      </c>
+      <c r="F47" t="n">
+        <v>39.3701</v>
+      </c>
+      <c r="G47" t="n">
+        <v>498.6877</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SARDEGNA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>15-30</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C48" t="n">
         <v>957.6271</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D48" t="n">
         <v>99.5763</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E48" t="n">
         <v>677.9661</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F48" t="n">
         <v>127.1186</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G48" t="n">
         <v>21.1864</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H48" t="n">
         <v>10.5932</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I48" t="n">
         <v>21.1864</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Tabella STPG pesata</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>segmento</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>classe_durata_soggiorno</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>totale</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>spese_trasporto_interno</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>spese_alloggio</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>spese_alimentazione</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>spese_ristorazione</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>spese_souvenir</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>spese_altre</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>SARDEGNA</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>1-3</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>15.399</v>
-      </c>
-      <c r="D49" t="n">
-        <v>2.212</v>
-      </c>
-      <c r="E49" t="n">
-        <v>3.9986</v>
-      </c>
-      <c r="F49" t="n">
-        <v>3.4031</v>
-      </c>
-      <c r="G49" t="n">
-        <v>2.212</v>
-      </c>
-      <c r="H49" t="n">
+      <c r="C52" t="n">
+        <v>14.9534</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2.9549</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.5072</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3.5817</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2.8653</v>
+      </c>
+      <c r="H52" t="n">
         <v>0</v>
       </c>
-      <c r="I49" t="n">
-        <v>3.5733</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="I52" t="n">
+        <v>3.0444</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>SARDEGNA</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>4-7</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>90</v>
+      </c>
+      <c r="D53" t="n">
+        <v>15</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>25</v>
+      </c>
+      <c r="G53" t="n">
+        <v>50</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SARDEGNA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>8-14</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C54" t="n">
         <v>64.4769</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D54" t="n">
         <v>0</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E54" t="n">
         <v>14.5985</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F54" t="n">
         <v>3.6496</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G54" t="n">
         <v>46.2287</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H54" t="n">
         <v>0</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I54" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>SARDEGNA</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>15-30</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C55" t="n">
         <v>40.7207</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D55" t="n">
         <v>4.2342</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E55" t="n">
         <v>28.8288</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F55" t="n">
         <v>5.4054</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G55" t="n">
         <v>0.9009</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H55" t="n">
         <v>0.4505</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I55" t="n">
         <v>0.9009</v>
       </c>
     </row>
